--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1532-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1532-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFE1FF62-1734-402D-98B7-2ECEE5EC37C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE48930F-A310-465F-9125-9534DB2393AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{2C91C30D-EA64-40AF-843A-1DC69963B9B0}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{1C1DFF34-2EB6-4044-AAB3-B524C7249050}"/>
   </bookViews>
   <sheets>
     <sheet name="1532-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1565,27 +1565,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2A590C0-53A7-4E39-AC05-F3E7D903A8C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D62497AD-50FF-4F75-BF93-7177999D93BB}">
   <dimension ref="A1:X40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1619,7 +1618,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1655,7 +1654,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1707,7 +1706,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1775,7 +1774,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1847,7 +1846,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1919,7 +1918,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1991,7 +1990,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2063,7 +2062,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2135,7 +2134,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2207,7 +2206,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2279,7 +2278,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2351,7 +2350,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2423,7 +2422,7 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2495,7 +2494,7 @@
         <v>8.86</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2567,7 +2566,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2639,7 +2638,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2711,7 +2710,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2783,7 +2782,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2855,7 +2854,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2927,7 +2926,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -2999,7 +2998,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3071,7 +3070,7 @@
         <v>9.2200000000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3143,7 +3142,7 @@
         <v>7.93</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3215,7 +3214,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3287,7 +3286,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2003</v>
       </c>
@@ -3359,7 +3358,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2002</v>
       </c>
@@ -3431,7 +3430,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2001</v>
       </c>
@@ -3503,7 +3502,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2000</v>
       </c>
@@ -3575,7 +3574,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>1999</v>
       </c>
@@ -3647,7 +3646,7 @@
         <v>9.7200000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>1998</v>
       </c>
@@ -3719,7 +3718,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>1997</v>
       </c>
@@ -3791,7 +3790,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="41">
         <v>1996</v>
       </c>
@@ -3863,7 +3862,7 @@
         <v>6.52</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="43"/>
       <c r="B34" s="44"/>
       <c r="C34" s="18" t="s">
@@ -3891,7 +3890,7 @@
       <c r="W34" s="50"/>
       <c r="X34" s="46"/>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="51">
         <v>1995</v>
       </c>
@@ -3963,7 +3962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="53"/>
       <c r="B36" s="54"/>
       <c r="C36" s="20" t="s">
@@ -3991,7 +3990,7 @@
       <c r="W36" s="60"/>
       <c r="X36" s="56"/>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1994</v>
       </c>
@@ -4063,7 +4062,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>1993</v>
       </c>
@@ -4135,7 +4134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1992</v>
       </c>
@@ -4207,7 +4206,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39" t="s">
         <v>57</v>
       </c>
